--- a/photography_forms/020_pre_wedding_videography_questionnaire--photography_forms.xlsx
+++ b/photography_forms/020_pre_wedding_videography_questionnaire--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'8-hour',_'label':_'8-hour'}</t>
+          <t>8-hour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '8-hour', 'label': '8-hour'}</t>
+          <t>8-hour</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'12-hour',_'label':_'12-hour'}</t>
+          <t>12-hour</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '12-hour', 'label': '12-hour'}</t>
+          <t>12-hour</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'16-hour',_'label':_'16-hour'}</t>
+          <t>16-hour</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '16-hour', 'label': '16-hour'}</t>
+          <t>16-hour</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -877,29 +877,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>special_requests_choices</t>
+          <t>location_and_layout_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>outdoor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>Outdoor</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'outdoor',_'label':_'outdoor'}</t>
+          <t>indoor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Outdoor', 'label': 'Outdoor'}</t>
+          <t>Indoor</t>
         </is>
       </c>
     </row>
@@ -928,29 +928,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'indoor',_'label':_'indoor'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Indoor', 'label': 'Indoor'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>location_and_layout_choices</t>
+          <t>review_preferences_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid', 'label': 'Hybrid'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -962,80 +962,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>review_preferences_choices</t>
+          <t>videographer_availability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>review_preferences_choices</t>
+          <t>videographer_availability_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>videographer_availability_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'value':_'available',_'label':_'available'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'value': 'Available', 'label': 'Available'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>videographer_availability_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'value':_'unavailable',_'label':_'unavailable'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'value': 'Unavailable', 'label': 'Unavailable'}</t>
+          <t>Unavailable</t>
         </is>
       </c>
     </row>
